--- a/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
+++ b/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="330" windowWidth="18120" windowHeight="7890"/>
+    <workbookView xWindow="0" yWindow="330" windowWidth="18120" windowHeight="7890" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="267">
   <si>
     <t>测试项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1083,6 +1083,18 @@
   </si>
   <si>
     <t>创建外表指定数据类型和实际插入数据类型不一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hashjoin/merge join/ nl join/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引sdb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{key:1.12e-15}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1315,6 +1327,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -1332,9 +1347,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1421,7 +1433,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1698,7 +1710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.375" customWidth="1"/>
@@ -1786,7 +1798,7 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="13" t="s">
         <v>209</v>
       </c>
       <c r="E5" t="s">
@@ -2319,10 +2331,13 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="54">
+      <c r="D62" t="s">
+        <v>264</v>
+      </c>
       <c r="E62" t="s">
         <v>94</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F62" s="13" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2513,171 +2528,176 @@
       </c>
     </row>
     <row r="84" spans="2:7">
-      <c r="B84" t="s">
+      <c r="C84" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7">
+      <c r="B85" t="s">
         <v>145</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C85" t="s">
         <v>146</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D85" t="s">
         <v>147</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F85" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="85" spans="2:7">
-      <c r="D85" t="s">
+    <row r="86" spans="2:7">
+      <c r="D86" t="s">
         <v>162</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F86" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="86" spans="2:7">
-      <c r="C86" t="s">
+    <row r="87" spans="2:7">
+      <c r="C87" t="s">
         <v>149</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F87" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="2:7" ht="108">
-      <c r="C87" t="s">
+    <row r="88" spans="2:7" ht="108">
+      <c r="C88" t="s">
         <v>151</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D88" t="s">
         <v>152</v>
       </c>
-      <c r="F87" s="19" t="s">
+      <c r="F88" s="13" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="88" spans="2:7" ht="27">
-      <c r="C88" t="s">
+    <row r="89" spans="2:7" ht="27">
+      <c r="C89" t="s">
         <v>154</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D89" t="s">
         <v>155</v>
       </c>
-      <c r="F88" s="19" t="s">
+      <c r="F89" s="13" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="89" spans="2:7">
-      <c r="D89" t="s">
+    <row r="90" spans="2:7">
+      <c r="D90" t="s">
         <v>157</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F90" t="s">
         <v>158</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7">
-      <c r="C90" t="s">
-        <v>159</v>
-      </c>
-      <c r="D90" t="s">
-        <v>160</v>
-      </c>
-      <c r="F90" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="91" spans="2:7">
       <c r="C91" t="s">
-        <v>177</v>
+        <v>159</v>
+      </c>
+      <c r="D91" t="s">
+        <v>160</v>
       </c>
       <c r="F91" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92" spans="2:7">
       <c r="C92" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F92" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="93" spans="2:7">
       <c r="C93" t="s">
+        <v>164</v>
+      </c>
+      <c r="F93" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7">
+      <c r="C94" t="s">
         <v>166</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D94" t="s">
         <v>172</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F94" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7">
-      <c r="D94" t="s">
-        <v>173</v>
-      </c>
-      <c r="F94" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="95" spans="2:7">
       <c r="D95" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F95" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="96" spans="2:7">
       <c r="D96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F96" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="D97" t="s">
+        <v>175</v>
+      </c>
+      <c r="F97" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="D98" t="s">
         <v>176</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F98" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="A98" t="s">
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
         <v>246</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B99" t="s">
         <v>251</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C99" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="C99" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="C100" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="C101" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
-      <c r="B101" t="s">
+    <row r="102" spans="1:6">
+      <c r="B102" t="s">
         <v>259</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C102" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
-      <c r="C102" t="s">
+    <row r="103" spans="1:6">
+      <c r="C103" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
-      <c r="A104" t="s">
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
         <v>255</v>
       </c>
     </row>
@@ -2698,7 +2718,7 @@
     <col min="3" max="3" width="38.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="40.5" thickBot="1">
+    <row r="1" spans="1:3" ht="15" thickBot="1">
       <c r="A1" s="4" t="s">
         <v>50</v>
       </c>
@@ -2710,11 +2730,11 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1">
       <c r="A3" s="6" t="s">
@@ -2738,7 +2758,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="29.25" thickBot="1">
+    <row r="5" spans="1:3" ht="15" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>14</v>
       </c>
@@ -2749,7 +2769,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="39" thickBot="1">
+    <row r="6" spans="1:3" ht="15" thickBot="1">
       <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
@@ -2760,7 +2780,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="39" thickBot="1">
+    <row r="7" spans="1:3" ht="15" thickBot="1">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
@@ -2771,7 +2791,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="29.25" thickBot="1">
+    <row r="8" spans="1:3" ht="15" thickBot="1">
       <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
@@ -2782,7 +2802,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="29.25" thickBot="1">
+    <row r="9" spans="1:3" ht="15" thickBot="1">
       <c r="A9" s="6" t="s">
         <v>62</v>
       </c>
@@ -2790,7 +2810,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>61</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1">
@@ -2804,7 +2824,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="29.25" thickBot="1">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
       <c r="A11" s="6" t="s">
         <v>25</v>
       </c>
@@ -2816,13 +2836,13 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
-    </row>
-    <row r="13" spans="1:3" ht="43.5" thickBot="1">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
       <c r="A13" s="6" t="s">
         <v>27</v>
       </c>
@@ -2833,7 +2853,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="43.5" thickBot="1">
+    <row r="14" spans="1:3" ht="15" thickBot="1">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -2844,7 +2864,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="43.5" thickBot="1">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
       <c r="A15" s="6" t="s">
         <v>31</v>
       </c>
@@ -2856,13 +2876,13 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="18"/>
-    </row>
-    <row r="17" spans="1:3" ht="40.5" thickBot="1">
+      <c r="B16" s="18"/>
+      <c r="C16" s="19"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
       <c r="A17" s="9" t="s">
         <v>33</v>
       </c>
@@ -2872,13 +2892,13 @@
       <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-    </row>
-    <row r="19" spans="1:3" ht="86.25" thickBot="1">
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
       <c r="A19" s="6" t="s">
         <v>35</v>
       </c>
@@ -2889,7 +2909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="43.5" thickBot="1">
+    <row r="20" spans="1:3" ht="15" thickBot="1">
       <c r="A20" s="11" t="s">
         <v>37</v>
       </c>
@@ -2907,7 +2927,7 @@
       </c>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" spans="1:3" ht="57.75" thickBot="1">
+    <row r="22" spans="1:3" ht="15" thickBot="1">
       <c r="A22" s="6" t="s">
         <v>39</v>
       </c>
@@ -2927,7 +2947,7 @@
       </c>
       <c r="C23" s="8"/>
     </row>
-    <row r="24" spans="1:3" ht="29.25" thickBot="1">
+    <row r="24" spans="1:3" ht="15" thickBot="1">
       <c r="A24" s="11" t="s">
         <v>42</v>
       </c>
@@ -2937,11 +2957,11 @@
       <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1">
       <c r="A26" s="6" t="s">

--- a/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
+++ b/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="330" windowWidth="18120" windowHeight="7890" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="330" windowWidth="18120" windowHeight="7890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="272">
   <si>
     <t>测试项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1086,15 +1086,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hashjoin/merge join/ nl join/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引sdb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{key:1.12e-15}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多表连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NESTED LOOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HASH JOIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SORT MERGE JOIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用sequoiadb索引字段查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查sequoiadb是否使用索引查询</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1433,7 +1453,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1710,7 +1730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.375" customWidth="1"/>
@@ -2331,9 +2351,6 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="54">
-      <c r="D62" t="s">
-        <v>264</v>
-      </c>
       <c r="E62" t="s">
         <v>94</v>
       </c>
@@ -2528,176 +2545,200 @@
       </c>
     </row>
     <row r="84" spans="2:7">
+      <c r="B84" t="s">
+        <v>145</v>
+      </c>
       <c r="C84" t="s">
-        <v>265</v>
+        <v>146</v>
+      </c>
+      <c r="D84" t="s">
+        <v>147</v>
+      </c>
+      <c r="F84" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="2:7">
-      <c r="B85" t="s">
-        <v>145</v>
-      </c>
-      <c r="C85" t="s">
-        <v>146</v>
-      </c>
       <c r="D85" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="F85" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="2:7">
-      <c r="D86" t="s">
-        <v>162</v>
+      <c r="C86" t="s">
+        <v>149</v>
       </c>
       <c r="F86" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" ht="108">
       <c r="C87" t="s">
-        <v>149</v>
-      </c>
-      <c r="F87" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" ht="108">
+        <v>151</v>
+      </c>
+      <c r="D87" t="s">
+        <v>152</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="27">
       <c r="C88" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D88" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7" ht="27">
-      <c r="C89" t="s">
-        <v>154</v>
-      </c>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7">
       <c r="D89" t="s">
-        <v>155</v>
-      </c>
-      <c r="F89" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="F89" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="90" spans="2:7">
+      <c r="C90" t="s">
+        <v>159</v>
+      </c>
       <c r="D90" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F90" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="91" spans="2:7">
       <c r="C91" t="s">
-        <v>159</v>
-      </c>
-      <c r="D91" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="F91" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="2:7">
       <c r="C92" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="F92" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="93" spans="2:7">
       <c r="C93" t="s">
-        <v>164</v>
+        <v>166</v>
+      </c>
+      <c r="D93" t="s">
+        <v>172</v>
       </c>
       <c r="F93" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="2:7">
-      <c r="C94" t="s">
-        <v>166</v>
-      </c>
       <c r="D94" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F94" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="95" spans="2:7">
       <c r="D95" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F95" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="2:7">
       <c r="D96" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F96" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="D97" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F97" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98" spans="1:6">
+      <c r="C98" t="s">
+        <v>265</v>
+      </c>
       <c r="D98" t="s">
-        <v>176</v>
-      </c>
-      <c r="F98" t="s">
-        <v>171</v>
+        <v>266</v>
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" t="s">
-        <v>246</v>
-      </c>
-      <c r="B99" t="s">
-        <v>251</v>
-      </c>
-      <c r="C99" t="s">
-        <v>252</v>
+      <c r="D99" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="100" spans="1:6">
-      <c r="C100" t="s">
-        <v>253</v>
+      <c r="D100" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="C101" t="s">
-        <v>254</v>
+        <v>269</v>
+      </c>
+      <c r="D101" t="s">
+        <v>270</v>
+      </c>
+      <c r="E101" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>246</v>
+      </c>
       <c r="B102" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C102" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="C103" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="C104" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="B105" t="s">
+        <v>259</v>
+      </c>
+      <c r="C105" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="C106" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
-      <c r="A105" t="s">
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
         <v>255</v>
       </c>
     </row>
@@ -2810,7 +2851,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1">

--- a/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
+++ b/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
@@ -15,8 +15,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+每种大类型覆盖一种运算符</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="270">
   <si>
     <t>测试项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -367,14 +403,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>更新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>查询</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -384,10 +412,6 @@
   </si>
   <si>
     <t>from子句</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连接表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -702,42 +726,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SELECT avg(num) FROM t1;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SELECT max(num) FROM t1;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SELECT min(num) FROM t1;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SELECT sum(num) FROM t1;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>count（）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>avg（）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max（）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>min（）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sum（）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NULL值匹配</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -790,10 +782,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对应sequoiadb类型：时间戳（pg查询自动加上时区）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>对应sequoiadb类型：不支持</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -930,191 +918,244 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>零为false，非零为true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖所有支持的数据类型、包括对应数据类型边界值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除单条记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新单条记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件批量更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新字段名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个PG连接器并发操作相同表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时插入数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时更新数据（包括相同和不相同数据）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时删除数据（包括相同和不相同数据）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时插入、更新、删除操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pg上多个表映射到sequoiadb同一个表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pg上多个表并发插入、更新、删除操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入操作对应sequoiadb映射表分别为：普通表、切分表、主子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据范围约束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb表中存在唯一索引，pg表中插入相同记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pg上插入数据不在子表范围内</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入数据过程中catalog节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入数据过程中data节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入数据过程中coord节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建外表指定IS NOT NULL约束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入数据过程中pg与sequoiadb网络异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询过程中pg与sequoiadb网络异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个pg的数据类型都需要验证sequoiadb中不支持的类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建外表指定数据类型和实际插入数据类型不一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{key:1.12e-15}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多表连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NESTED LOOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HASH JOIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SORT MERGE JOIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用sequoiadb索引字段查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查sequoiadb是否使用索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pg对应sequoiadb数据类型、对应类型边界值（更新、删除）；不支持的数据类型（任取一种验证）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖所有支持的数据类型、包括对应数据类型边界值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pg对应sequoiadb数据类型、对应类型边界值；不支持的数据类型（任取一种验证）；支持的所有运算符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建外表不指定IS NOT NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>连接表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（外表和内表、外表和外表）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新（单机和集群）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除（单机和集群模式）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单机只验证基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个coord连接，已连接coord异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>sequoiaDB中数据类型为整数，postgreSQL中映射类型为布尔类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>零为false，非零为true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>覆盖所有支持的数据类型、包括对应数据类型边界值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除单条记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>带条件删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新单条记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>带条件批量更新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新字段名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多个PG连接器并发操作相同表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>并发操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同时插入数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同时更新数据（包括相同和不相同数据）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同时删除数据（包括相同和不相同数据）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同时插入、更新、删除操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pg上多个表映射到sequoiadb同一个表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pg上多个表并发插入、更新、删除操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入操作对应sequoiadb映射表分别为：普通表、切分表、主子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据范围约束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb表中存在唯一索引，pg表中插入相同记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pg上插入数据不在子表范围内</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入数据过程中catalog节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入数据过程中data节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入数据过程中coord节点异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fdw配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建外表指定IS NOT NULL约束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建外表不指定IS NOT NULL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入数据过程中pg与sequoiadb网络异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询过程中pg与sequoiadb网络异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个pg的数据类型都需要验证sequoiadb中不支持的类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建外表指定数据类型和实际插入数据类型不一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{key:1.12e-15}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多表连接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NESTED LOOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HASH JOIN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SORT MERGE JOIN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb索引查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用sequoiadb索引字段查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检查sequoiadb是否使用索引查询</t>
+    <t>sequoiaDB中数据类型为timestamp，postgreSQL中映射类型为timestamp with time zone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前不支持该功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1122,7 +1163,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1206,6 +1247,29 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1227,7 +1291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1311,11 +1375,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFFC000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1368,6 +1441,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1730,14 +1804,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.375" customWidth="1"/>
-    <col min="2" max="2" width="27.25" customWidth="1"/>
-    <col min="3" max="3" width="26.75" customWidth="1"/>
-    <col min="4" max="4" width="49.75" customWidth="1"/>
-    <col min="5" max="5" width="68.125" customWidth="1"/>
+    <col min="1" max="1" width="7.25" customWidth="1"/>
+    <col min="2" max="2" width="10.5" customWidth="1"/>
+    <col min="3" max="3" width="14.25" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="8.375" customWidth="1"/>
     <col min="6" max="6" width="67.25" customWidth="1"/>
     <col min="7" max="7" width="78.375" customWidth="1"/>
   </cols>
@@ -1776,10 +1850,10 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="2"/>
@@ -1790,14 +1864,14 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E3" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1806,10 +1880,10 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="2"/>
@@ -1819,10 +1893,10 @@
         <v>17</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="2"/>
@@ -1832,13 +1906,13 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1846,10 +1920,10 @@
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -1858,10 +1932,10 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1869,10 +1943,10 @@
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E9" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1880,10 +1954,10 @@
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1894,10 +1968,10 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E11" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1905,10 +1979,10 @@
         <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1916,10 +1990,10 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1930,10 +2004,10 @@
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F14" s="3"/>
     </row>
@@ -1945,10 +2019,10 @@
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E15" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1956,10 +2030,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
-      </c>
-      <c r="E16" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="2:6">
@@ -1967,10 +2038,10 @@
         <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E17" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -1978,7 +2049,7 @@
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="2:6">
@@ -1986,7 +2057,7 @@
         <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="2:6">
@@ -1994,7 +2065,7 @@
         <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:6">
@@ -2005,7 +2076,7 @@
         <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -2016,7 +2087,7 @@
         <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="2:6">
@@ -2027,7 +2098,7 @@
         <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F23" t="s">
         <v>84</v>
@@ -2035,717 +2106,709 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C24" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D24" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D25" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C26" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D26" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C27" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="D27" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C28" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D28" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="C29" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D29" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D30" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D31" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="B33" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="B34" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="20" customFormat="1">
+      <c r="B35" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" t="s">
+        <v>201</v>
+      </c>
+      <c r="C36" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" t="s">
+        <v>204</v>
+      </c>
+      <c r="E36" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="C37" t="s">
         <v>205</v>
       </c>
-      <c r="D32" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="B33" t="s">
+      <c r="D37" t="s">
         <v>206</v>
       </c>
-      <c r="D33" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="B34" t="s">
+      <c r="E37" t="s">
         <v>207</v>
       </c>
-      <c r="D34" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="B35" t="s">
-        <v>208</v>
-      </c>
-      <c r="D35" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
-        <v>220</v>
-      </c>
-      <c r="B36" t="s">
+    </row>
+    <row r="38" spans="1:7">
+      <c r="D38" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="D39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="D40" t="s">
+        <v>267</v>
+      </c>
+      <c r="F40" t="s">
         <v>213</v>
       </c>
-      <c r="C36" t="s">
-        <v>214</v>
-      </c>
-      <c r="D36" t="s">
-        <v>216</v>
-      </c>
-      <c r="E36" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="C37" t="s">
-        <v>217</v>
-      </c>
-      <c r="D37" t="s">
-        <v>218</v>
-      </c>
-      <c r="E37" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="D38" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="D39" t="s">
+    </row>
+    <row r="41" spans="1:7">
+      <c r="B41" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" t="s">
+        <v>211</v>
+      </c>
+      <c r="E41" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="B42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G42" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="C43" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="C44" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="B45" t="s">
+        <v>235</v>
+      </c>
+      <c r="C45" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="C46" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="B47" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" t="s">
         <v>225</v>
       </c>
-      <c r="F39" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="B40" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" t="s">
-        <v>223</v>
-      </c>
-      <c r="E40" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="B41" t="s">
-        <v>256</v>
-      </c>
-      <c r="C41" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="C42" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="C43" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="B44" t="s">
-        <v>248</v>
-      </c>
-      <c r="C44" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="C45" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="B46" t="s">
-        <v>239</v>
-      </c>
-      <c r="C46" t="s">
-        <v>238</v>
-      </c>
-      <c r="D46" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
       <c r="D47" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="D48" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="D49" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="C50" t="s">
-        <v>244</v>
-      </c>
       <c r="D50" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="C51" t="s">
+        <v>231</v>
+      </c>
+      <c r="D51" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="20" customFormat="1"/>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
         <v>85</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
         <v>86</v>
       </c>
-      <c r="D52" t="s">
-        <v>247</v>
-      </c>
-      <c r="E52" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" t="s">
-        <v>235</v>
+      <c r="D53" t="s">
+        <v>234</v>
       </c>
       <c r="E53" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:6">
+      <c r="B54" t="s">
+        <v>263</v>
+      </c>
       <c r="C54" t="s">
-        <v>236</v>
+        <v>222</v>
+      </c>
+      <c r="E54" t="s">
+        <v>258</v>
+      </c>
+      <c r="F54" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="C55" t="s">
-        <v>237</v>
-      </c>
-      <c r="D55" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:6">
+      <c r="C56" t="s">
+        <v>224</v>
+      </c>
       <c r="D56" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="B57" t="s">
-        <v>88</v>
-      </c>
-      <c r="C57" t="s">
-        <v>228</v>
+      <c r="D57" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:6">
+      <c r="B58" t="s">
+        <v>264</v>
+      </c>
       <c r="C58" t="s">
-        <v>229</v>
+        <v>215</v>
+      </c>
+      <c r="F58" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="C59" t="s">
-        <v>230</v>
-      </c>
-      <c r="D59" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" spans="1:6">
+      <c r="C60" t="s">
+        <v>217</v>
+      </c>
       <c r="D60" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" s="20" customFormat="1">
+      <c r="D61" s="20" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" t="s">
         <v>89</v>
       </c>
-      <c r="B61" t="s">
+      <c r="D62" t="s">
+        <v>261</v>
+      </c>
+      <c r="E62" t="s">
         <v>90</v>
       </c>
-      <c r="C61" t="s">
+      <c r="F62" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="54">
+      <c r="E63" t="s">
         <v>91</v>
       </c>
-      <c r="D61" t="s">
+      <c r="F63" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="E64" t="s">
         <v>92</v>
       </c>
-      <c r="E61" t="s">
-        <v>93</v>
-      </c>
-      <c r="F61" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="54">
-      <c r="E62" t="s">
-        <v>94</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="E63" t="s">
-        <v>95</v>
-      </c>
-      <c r="F63" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="D64" t="s">
-        <v>96</v>
-      </c>
       <c r="F64" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="2:7">
       <c r="D65" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F65" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="2:7">
       <c r="D66" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="F66" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="2:7">
       <c r="D67" t="s">
-        <v>99</v>
-      </c>
-      <c r="F67" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="2:7">
-      <c r="C68" t="s">
-        <v>106</v>
+      <c r="D68" t="s">
+        <v>96</v>
       </c>
       <c r="F68" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="2:7">
       <c r="C69" t="s">
+        <v>103</v>
+      </c>
+      <c r="F69" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7">
+      <c r="C70" t="s">
+        <v>105</v>
+      </c>
+      <c r="D70" t="s">
+        <v>106</v>
+      </c>
+      <c r="F70" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7">
+      <c r="D71" t="s">
         <v>108</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F71" t="s">
         <v>109</v>
       </c>
-      <c r="F69" t="s">
+    </row>
+    <row r="72" spans="2:7">
+      <c r="C72" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="70" spans="2:7">
-      <c r="D70" t="s">
+    <row r="73" spans="2:7">
+      <c r="B73" t="s">
         <v>111</v>
       </c>
-      <c r="F70" t="s">
+      <c r="C73" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="71" spans="2:7">
-      <c r="C71" t="s">
+      <c r="F73" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7">
-      <c r="B72" t="s">
-        <v>114</v>
-      </c>
-      <c r="C72" t="s">
-        <v>115</v>
-      </c>
-      <c r="F72" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7">
-      <c r="C73" t="s">
-        <v>117</v>
-      </c>
-      <c r="F73" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="74" spans="2:7">
       <c r="C74" t="s">
+        <v>114</v>
+      </c>
+      <c r="F74" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7">
+      <c r="C75" t="s">
+        <v>116</v>
+      </c>
+      <c r="F75" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7">
+      <c r="B76" t="s">
+        <v>118</v>
+      </c>
+      <c r="C76" t="s">
+        <v>122</v>
+      </c>
+      <c r="F76" t="s">
+        <v>123</v>
+      </c>
+      <c r="G76" t="s">
         <v>119</v>
-      </c>
-      <c r="F74" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7">
-      <c r="B75" t="s">
-        <v>121</v>
-      </c>
-      <c r="C75" t="s">
-        <v>125</v>
-      </c>
-      <c r="F75" t="s">
-        <v>126</v>
-      </c>
-      <c r="G75" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7">
-      <c r="C76" t="s">
-        <v>123</v>
-      </c>
-      <c r="F76" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="77" spans="2:7">
       <c r="C77" t="s">
+        <v>120</v>
+      </c>
+      <c r="F77" t="s">
         <v>124</v>
       </c>
-      <c r="F77" t="s">
-        <v>128</v>
-      </c>
     </row>
     <row r="78" spans="2:7">
-      <c r="B78" t="s">
-        <v>129</v>
-      </c>
       <c r="C78" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F78" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="2:7">
       <c r="B79" t="s">
+        <v>126</v>
+      </c>
+      <c r="C79" t="s">
+        <v>127</v>
+      </c>
+      <c r="F79" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7">
+      <c r="B80" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" t="s">
         <v>132</v>
       </c>
-      <c r="C79" t="s">
+      <c r="F80" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7">
+      <c r="C81" t="s">
+        <v>133</v>
+      </c>
+      <c r="F81" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7">
+      <c r="B82" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C82" t="s">
         <v>135</v>
       </c>
-      <c r="F79" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="80" spans="2:7">
-      <c r="C80" t="s">
+      <c r="G82" t="s">
         <v>136</v>
       </c>
-      <c r="F80" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7">
-      <c r="B81" s="2" t="s">
+    </row>
+    <row r="83" spans="2:7">
+      <c r="B83" t="s">
         <v>137</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C83" t="s">
+        <v>140</v>
+      </c>
+      <c r="F83" t="s">
         <v>138</v>
       </c>
-      <c r="G81" t="s">
+    </row>
+    <row r="84" spans="2:7">
+      <c r="C84" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="82" spans="2:7">
-      <c r="B82" t="s">
-        <v>140</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="F84" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7">
+      <c r="B85" t="s">
+        <v>142</v>
+      </c>
+      <c r="C85" t="s">
         <v>143</v>
       </c>
-      <c r="F82" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7">
-      <c r="C83" t="s">
-        <v>142</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="D85" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="84" spans="2:7">
-      <c r="B84" t="s">
+      <c r="F85" t="s">
         <v>145</v>
       </c>
-      <c r="C84" t="s">
+    </row>
+    <row r="86" spans="2:7">
+      <c r="D86" t="s">
+        <v>159</v>
+      </c>
+      <c r="F86" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7">
+      <c r="C87" t="s">
         <v>146</v>
       </c>
-      <c r="D84" t="s">
+      <c r="F87" t="s">
         <v>147</v>
       </c>
-      <c r="F84" t="s">
+    </row>
+    <row r="88" spans="2:7" ht="108">
+      <c r="C88" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="85" spans="2:7">
-      <c r="D85" t="s">
-        <v>162</v>
-      </c>
-      <c r="F85" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7">
-      <c r="C86" t="s">
+      <c r="D88" t="s">
         <v>149</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F88" s="13" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="2:7" ht="108">
-      <c r="C87" t="s">
+    <row r="89" spans="2:7" ht="27">
+      <c r="C89" t="s">
         <v>151</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D89" t="s">
         <v>152</v>
       </c>
-      <c r="F87" s="13" t="s">
+      <c r="F89" s="13" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="88" spans="2:7" ht="27">
-      <c r="C88" t="s">
+    <row r="90" spans="2:7">
+      <c r="D90" t="s">
         <v>154</v>
       </c>
-      <c r="D88" t="s">
+      <c r="F90" t="s">
         <v>155</v>
-      </c>
-      <c r="F88" s="13" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7">
-      <c r="D89" t="s">
-        <v>157</v>
-      </c>
-      <c r="F89" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7">
-      <c r="C90" t="s">
-        <v>159</v>
-      </c>
-      <c r="D90" t="s">
-        <v>160</v>
-      </c>
-      <c r="F90" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="91" spans="2:7">
       <c r="C91" t="s">
-        <v>177</v>
+        <v>156</v>
+      </c>
+      <c r="D91" t="s">
+        <v>157</v>
       </c>
       <c r="F91" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="92" spans="2:7">
       <c r="C92" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F92" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="2:7">
       <c r="C93" t="s">
-        <v>166</v>
-      </c>
-      <c r="D93" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F93" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="94" spans="2:7">
+      <c r="C94" t="s">
+        <v>163</v>
+      </c>
       <c r="D94" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F94" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="95" spans="2:7">
+      <c r="C95" t="s">
+        <v>250</v>
+      </c>
       <c r="D95" t="s">
-        <v>174</v>
-      </c>
-      <c r="F95" t="s">
-        <v>169</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" spans="2:7">
       <c r="D96" t="s">
-        <v>175</v>
-      </c>
-      <c r="F96" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="D97" t="s">
-        <v>176</v>
-      </c>
-      <c r="F97" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="C98" t="s">
-        <v>265</v>
-      </c>
-      <c r="D98" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" s="20" customFormat="1">
+      <c r="C98" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="D98" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>233</v>
+      </c>
+      <c r="B99" t="s">
+        <v>238</v>
+      </c>
+      <c r="C99" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="C100" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="C101" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="B102" t="s">
+        <v>244</v>
+      </c>
+      <c r="C102" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="C103" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" s="20" customFormat="1">
+      <c r="C104" s="20" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
-      <c r="D99" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="D100" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="C101" t="s">
-        <v>269</v>
-      </c>
-      <c r="D101" t="s">
-        <v>270</v>
-      </c>
-      <c r="E101" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102" t="s">
-        <v>246</v>
-      </c>
-      <c r="B102" t="s">
-        <v>251</v>
-      </c>
-      <c r="C102" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="C103" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="C104" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="B105" t="s">
-        <v>259</v>
-      </c>
-      <c r="C105" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="C106" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108" t="s">
-        <v>255</v>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2851,7 +2914,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1">

--- a/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
+++ b/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="273">
   <si>
     <t>测试项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1156,6 +1156,18 @@
   </si>
   <si>
     <t>目前不支持该功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邓强中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1804,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.25" customWidth="1"/>
@@ -1813,10 +1825,11 @@
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="8.375" customWidth="1"/>
     <col min="6" max="6" width="67.25" customWidth="1"/>
-    <col min="7" max="7" width="78.375" customWidth="1"/>
+    <col min="7" max="7" width="13.375" customWidth="1"/>
+    <col min="8" max="8" width="78.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1836,10 +1849,13 @@
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1856,9 +1872,12 @@
         <v>257</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="B3" s="3"/>
       <c r="C3" t="s">
         <v>13</v>
@@ -1870,11 +1889,12 @@
         <v>200</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="2" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="B4" s="3"/>
       <c r="C4" t="s">
         <v>15</v>
@@ -1886,9 +1906,10 @@
         <v>200</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="27">
+      <c r="G4" s="3"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="40.5">
       <c r="C5" t="s">
         <v>17</v>
       </c>
@@ -1899,9 +1920,10 @@
         <v>259</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="G5" s="3"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="C6" t="s">
         <v>19</v>
       </c>
@@ -1911,11 +1933,11 @@
       <c r="E6" t="s">
         <v>200</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="C7" t="s">
         <v>21</v>
       </c>
@@ -1925,9 +1947,9 @@
       <c r="E7" t="s">
         <v>200</v>
       </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="C8" t="s">
         <v>22</v>
       </c>
@@ -1938,7 +1960,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="C9" t="s">
         <v>24</v>
       </c>
@@ -1949,7 +1971,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="C10" t="s">
         <v>26</v>
       </c>
@@ -1960,7 +1982,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="B11" t="s">
         <v>78</v>
       </c>
@@ -1974,7 +1996,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="C12" t="s">
         <v>28</v>
       </c>
@@ -1985,7 +2007,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="C13" t="s">
         <v>32</v>
       </c>
@@ -1996,7 +2018,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="B14" t="s">
         <v>79</v>
       </c>
@@ -2010,8 +2032,9 @@
         <v>200</v>
       </c>
       <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="B15" t="s">
         <v>80</v>
       </c>
@@ -2025,7 +2048,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="C16" t="s">
         <v>38</v>
       </c>
@@ -2191,7 +2214,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:8">
       <c r="B33" t="s">
         <v>194</v>
       </c>
@@ -2199,7 +2222,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:8">
       <c r="B34" t="s">
         <v>195</v>
       </c>
@@ -2207,7 +2230,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="20" customFormat="1">
+    <row r="35" spans="1:8" s="20" customFormat="1">
       <c r="B35" s="20" t="s">
         <v>196</v>
       </c>
@@ -2215,7 +2238,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>208</v>
       </c>
@@ -2231,8 +2254,11 @@
       <c r="E36" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="G36" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="C37" t="s">
         <v>205</v>
       </c>
@@ -2243,17 +2269,17 @@
         <v>207</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:8">
       <c r="D38" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:8">
       <c r="D39" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:8">
       <c r="D40" t="s">
         <v>267</v>
       </c>
@@ -2261,7 +2287,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:8">
       <c r="B41" t="s">
         <v>209</v>
       </c>
@@ -2272,31 +2298,31 @@
         <v>210</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:8">
       <c r="B42" t="s">
         <v>242</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:8">
       <c r="C43" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:8">
       <c r="C44" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:8">
       <c r="B45" t="s">
         <v>235</v>
       </c>
@@ -2304,12 +2330,12 @@
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:8">
       <c r="C46" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:8">
       <c r="B47" t="s">
         <v>226</v>
       </c>
@@ -2320,22 +2346,22 @@
         <v>227</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:8">
       <c r="D48" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:7">
       <c r="D49" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:7">
       <c r="D50" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:7">
       <c r="C51" t="s">
         <v>231</v>
       </c>
@@ -2343,8 +2369,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="52" spans="1:6" s="20" customFormat="1"/>
-    <row r="53" spans="1:6">
+    <row r="52" spans="1:7" s="20" customFormat="1"/>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>85</v>
       </c>
@@ -2357,8 +2383,11 @@
       <c r="E53" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="B54" t="s">
         <v>263</v>
       </c>
@@ -2372,12 +2401,12 @@
         <v>265</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:7">
       <c r="C55" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:7">
       <c r="C56" t="s">
         <v>224</v>
       </c>
@@ -2385,12 +2414,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:7">
       <c r="D57" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:7">
       <c r="B58" t="s">
         <v>264</v>
       </c>
@@ -2401,12 +2430,12 @@
         <v>265</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:7">
       <c r="C59" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:7">
       <c r="C60" t="s">
         <v>217</v>
       </c>
@@ -2414,12 +2443,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="61" spans="1:6" s="20" customFormat="1">
+    <row r="61" spans="1:7" s="20" customFormat="1">
       <c r="D61" s="20" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>87</v>
       </c>
@@ -2439,15 +2468,16 @@
         <v>97</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="54">
+    <row r="63" spans="1:7" ht="54">
       <c r="E63" t="s">
         <v>91</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63" s="13"/>
+    </row>
+    <row r="64" spans="1:7">
       <c r="E64" t="s">
         <v>92</v>
       </c>
@@ -2455,7 +2485,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="2:7">
+    <row r="65" spans="2:8">
       <c r="D65" t="s">
         <v>93</v>
       </c>
@@ -2463,7 +2493,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="2:7">
+    <row r="66" spans="2:8">
       <c r="D66" t="s">
         <v>94</v>
       </c>
@@ -2471,12 +2501,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="67" spans="2:7">
+    <row r="67" spans="2:8">
       <c r="D67" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="68" spans="2:7">
+    <row r="68" spans="2:8">
       <c r="D68" t="s">
         <v>96</v>
       </c>
@@ -2484,7 +2514,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="2:7">
+    <row r="69" spans="2:8">
       <c r="C69" t="s">
         <v>103</v>
       </c>
@@ -2492,7 +2522,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="70" spans="2:7">
+    <row r="70" spans="2:8">
       <c r="C70" t="s">
         <v>105</v>
       </c>
@@ -2503,7 +2533,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="71" spans="2:7">
+    <row r="71" spans="2:8">
       <c r="D71" t="s">
         <v>108</v>
       </c>
@@ -2511,12 +2541,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="2:7">
+    <row r="72" spans="2:8">
       <c r="C72" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="73" spans="2:7">
+    <row r="73" spans="2:8">
       <c r="B73" t="s">
         <v>111</v>
       </c>
@@ -2527,7 +2557,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="74" spans="2:7">
+    <row r="74" spans="2:8">
       <c r="C74" t="s">
         <v>114</v>
       </c>
@@ -2535,7 +2565,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="75" spans="2:7">
+    <row r="75" spans="2:8">
       <c r="C75" t="s">
         <v>116</v>
       </c>
@@ -2543,7 +2573,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="2:7">
+    <row r="76" spans="2:8">
       <c r="B76" t="s">
         <v>118</v>
       </c>
@@ -2553,11 +2583,11 @@
       <c r="F76" t="s">
         <v>123</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="77" spans="2:7">
+    <row r="77" spans="2:8">
       <c r="C77" t="s">
         <v>120</v>
       </c>
@@ -2565,7 +2595,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="78" spans="2:7">
+    <row r="78" spans="2:8">
       <c r="C78" t="s">
         <v>121</v>
       </c>
@@ -2573,7 +2603,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="79" spans="2:7">
+    <row r="79" spans="2:8">
       <c r="B79" t="s">
         <v>126</v>
       </c>
@@ -2584,7 +2614,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="80" spans="2:7">
+    <row r="80" spans="2:8">
       <c r="B80" t="s">
         <v>129</v>
       </c>
@@ -2595,7 +2625,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="81" spans="2:7">
+    <row r="81" spans="2:8">
       <c r="C81" t="s">
         <v>133</v>
       </c>
@@ -2603,18 +2633,18 @@
         <v>131</v>
       </c>
     </row>
-    <row r="82" spans="2:7">
+    <row r="82" spans="2:8">
       <c r="B82" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C82" t="s">
         <v>135</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="83" spans="2:7">
+    <row r="83" spans="2:8">
       <c r="B83" t="s">
         <v>137</v>
       </c>
@@ -2625,7 +2655,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="84" spans="2:7">
+    <row r="84" spans="2:8">
       <c r="C84" t="s">
         <v>139</v>
       </c>
@@ -2633,7 +2663,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="85" spans="2:7">
+    <row r="85" spans="2:8">
       <c r="B85" t="s">
         <v>142</v>
       </c>
@@ -2647,7 +2677,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="86" spans="2:7">
+    <row r="86" spans="2:8">
       <c r="D86" t="s">
         <v>159</v>
       </c>
@@ -2655,7 +2685,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="87" spans="2:7">
+    <row r="87" spans="2:8">
       <c r="C87" t="s">
         <v>146</v>
       </c>
@@ -2663,7 +2693,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="88" spans="2:7" ht="108">
+    <row r="88" spans="2:8" ht="108">
       <c r="C88" t="s">
         <v>148</v>
       </c>
@@ -2673,8 +2703,9 @@
       <c r="F88" s="13" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="89" spans="2:7" ht="27">
+      <c r="G88" s="13"/>
+    </row>
+    <row r="89" spans="2:8" ht="27">
       <c r="C89" t="s">
         <v>151</v>
       </c>
@@ -2684,8 +2715,9 @@
       <c r="F89" s="13" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="90" spans="2:7">
+      <c r="G89" s="13"/>
+    </row>
+    <row r="90" spans="2:8">
       <c r="D90" t="s">
         <v>154</v>
       </c>
@@ -2693,7 +2725,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="91" spans="2:7">
+    <row r="91" spans="2:8">
       <c r="C91" t="s">
         <v>156</v>
       </c>
@@ -2704,7 +2736,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="92" spans="2:7">
+    <row r="92" spans="2:8">
       <c r="C92" t="s">
         <v>166</v>
       </c>
@@ -2712,7 +2744,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="93" spans="2:7">
+    <row r="93" spans="2:8">
       <c r="C93" t="s">
         <v>161</v>
       </c>
@@ -2720,7 +2752,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="94" spans="2:7">
+    <row r="94" spans="2:8">
       <c r="C94" t="s">
         <v>163</v>
       </c>
@@ -2731,7 +2763,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="95" spans="2:7">
+    <row r="95" spans="2:8">
       <c r="C95" t="s">
         <v>250</v>
       </c>
@@ -2739,7 +2771,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="96" spans="2:7">
+    <row r="96" spans="2:8">
       <c r="D96" t="s">
         <v>252</v>
       </c>

--- a/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
+++ b/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
@@ -922,10 +922,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>覆盖所有支持的数据类型、包括对应数据类型边界值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>删除表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1168,6 +1164,10 @@
   </si>
   <si>
     <t>邓强中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖所有支持的数据类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1435,6 +1435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -1453,81 +1454,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1539,7 +1471,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1849,7 +1781,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>5</v>
@@ -1869,11 +1801,11 @@
         <v>168</v>
       </c>
       <c r="E2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H2" s="2"/>
     </row>
@@ -1891,7 +1823,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1917,7 +1849,7 @@
         <v>197</v>
       </c>
       <c r="E5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -2230,11 +2162,11 @@
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="20" customFormat="1">
-      <c r="B35" s="20" t="s">
+    <row r="35" spans="1:8" s="14" customFormat="1">
+      <c r="B35" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="14" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2255,7 +2187,7 @@
         <v>203</v>
       </c>
       <c r="G36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2276,12 +2208,12 @@
     </row>
     <row r="39" spans="1:8">
       <c r="D39" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="D40" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F40" t="s">
         <v>213</v>
@@ -2300,76 +2232,76 @@
     </row>
     <row r="42" spans="1:8">
       <c r="B42" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="H42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="C43" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="C44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="B45" t="s">
+        <v>234</v>
+      </c>
+      <c r="C45" t="s">
         <v>235</v>
-      </c>
-      <c r="C45" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="C46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="B47" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" t="s">
+        <v>224</v>
+      </c>
+      <c r="D47" t="s">
         <v>226</v>
-      </c>
-      <c r="C47" t="s">
-        <v>225</v>
-      </c>
-      <c r="D47" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="D49" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="D50" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="C51" t="s">
+        <v>230</v>
+      </c>
+      <c r="D51" t="s">
         <v>231</v>
       </c>
-      <c r="D51" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="20" customFormat="1"/>
+    </row>
+    <row r="52" spans="1:7" s="14" customFormat="1"/>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>85</v>
@@ -2378,74 +2310,74 @@
         <v>86</v>
       </c>
       <c r="D53" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E53" t="s">
-        <v>214</v>
+        <v>272</v>
       </c>
       <c r="G53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="B54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C54" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E54" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="C55" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="C56" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D56" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="D57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="B58" t="s">
+        <v>263</v>
+      </c>
+      <c r="C58" t="s">
+        <v>214</v>
+      </c>
+      <c r="F58" t="s">
         <v>264</v>
-      </c>
-      <c r="C58" t="s">
-        <v>215</v>
-      </c>
-      <c r="F58" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="C59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="C60" t="s">
+        <v>216</v>
+      </c>
+      <c r="D60" t="s">
         <v>217</v>
       </c>
-      <c r="D60" t="s">
+    </row>
+    <row r="61" spans="1:7" s="14" customFormat="1">
+      <c r="D61" s="14" t="s">
         <v>218</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" s="20" customFormat="1">
-      <c r="D61" s="20" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2459,7 +2391,7 @@
         <v>89</v>
       </c>
       <c r="D62" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E62" t="s">
         <v>90</v>
@@ -2765,75 +2697,75 @@
     </row>
     <row r="95" spans="2:8">
       <c r="C95" t="s">
+        <v>249</v>
+      </c>
+      <c r="D95" t="s">
         <v>250</v>
-      </c>
-      <c r="D95" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="96" spans="2:8">
       <c r="D96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="D97" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" s="14" customFormat="1">
+      <c r="C98" s="14" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" s="20" customFormat="1">
-      <c r="C98" s="20" t="s">
+      <c r="D98" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="D98" s="20" t="s">
+      <c r="E98" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="E98" s="20" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B99" t="s">
+        <v>237</v>
+      </c>
+      <c r="C99" t="s">
         <v>238</v>
-      </c>
-      <c r="C99" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="C100" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="C101" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="B102" t="s">
+        <v>243</v>
+      </c>
+      <c r="C102" t="s">
         <v>244</v>
-      </c>
-      <c r="C102" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="C103" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" s="20" customFormat="1">
-      <c r="C104" s="20" t="s">
-        <v>266</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" s="14" customFormat="1">
+      <c r="C104" s="14" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -2866,11 +2798,11 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1">
       <c r="A3" s="6" t="s">
@@ -2946,7 +2878,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1">
@@ -2972,11 +2904,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1">
       <c r="A13" s="6" t="s">
@@ -3012,11 +2944,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
     </row>
     <row r="17" spans="1:3" ht="15" thickBot="1">
       <c r="A17" s="9" t="s">
@@ -3028,11 +2960,11 @@
       <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1">
       <c r="A19" s="6" t="s">
@@ -3093,11 +3025,11 @@
       <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1">
       <c r="A26" s="6" t="s">

--- a/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
+++ b/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="275">
   <si>
     <t>测试项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1168,6 +1168,14 @@
   </si>
   <si>
     <t>覆盖所有支持的数据类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1400,7 +1408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1453,6 +1461,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1751,12 +1768,12 @@
   <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="7.25" customWidth="1"/>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="9.25" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="14.25" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="8.375" customWidth="1"/>
-    <col min="6" max="6" width="67.25" customWidth="1"/>
+    <col min="6" max="6" width="70.625" style="13" customWidth="1"/>
     <col min="7" max="7" width="13.375" customWidth="1"/>
     <col min="8" max="8" width="78.375" customWidth="1"/>
   </cols>
@@ -1777,7 +1794,7 @@
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="21" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1803,7 +1820,7 @@
       <c r="E2" t="s">
         <v>256</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="22"/>
       <c r="G2" s="3" t="s">
         <v>270</v>
       </c>
@@ -1820,7 +1837,7 @@
       <c r="E3" t="s">
         <v>200</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="3"/>
       <c r="H3" s="2" t="s">
         <v>246</v>
@@ -1837,7 +1854,7 @@
       <c r="E4" t="s">
         <v>200</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="3"/>
       <c r="H4" s="2"/>
     </row>
@@ -1851,7 +1868,7 @@
       <c r="E5" t="s">
         <v>258</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="22"/>
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
     </row>
@@ -1963,7 +1980,7 @@
       <c r="E14" t="s">
         <v>200</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="22"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:8">
@@ -2055,7 +2072,7 @@
       <c r="D23" t="s">
         <v>177</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="13" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2169,6 +2186,7 @@
       <c r="D35" s="14" t="s">
         <v>179</v>
       </c>
+      <c r="F35" s="23"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
@@ -2215,7 +2233,7 @@
       <c r="D40" t="s">
         <v>266</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="13" t="s">
         <v>213</v>
       </c>
     </row>
@@ -2301,7 +2319,9 @@
         <v>231</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="14" customFormat="1"/>
+    <row r="52" spans="1:7" s="14" customFormat="1">
+      <c r="F52" s="23"/>
+    </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>85</v>
@@ -2329,7 +2349,7 @@
       <c r="E54" t="s">
         <v>257</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="13" t="s">
         <v>264</v>
       </c>
     </row>
@@ -2358,7 +2378,7 @@
       <c r="C58" t="s">
         <v>214</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="13" t="s">
         <v>264</v>
       </c>
     </row>
@@ -2379,6 +2399,7 @@
       <c r="D61" s="14" t="s">
         <v>218</v>
       </c>
+      <c r="F61" s="23"/>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
@@ -2396,8 +2417,11 @@
       <c r="E62" t="s">
         <v>90</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="13" t="s">
         <v>97</v>
+      </c>
+      <c r="G62" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="54">
@@ -2413,7 +2437,7 @@
       <c r="E64" t="s">
         <v>92</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="13" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2421,7 +2445,7 @@
       <c r="D65" t="s">
         <v>93</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="13" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2429,7 +2453,7 @@
       <c r="D66" t="s">
         <v>94</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="13" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2438,11 +2462,11 @@
         <v>95</v>
       </c>
     </row>
-    <row r="68" spans="2:8">
+    <row r="68" spans="2:8" ht="27">
       <c r="D68" t="s">
         <v>96</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="13" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2450,7 +2474,7 @@
       <c r="C69" t="s">
         <v>103</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="13" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2461,7 +2485,7 @@
       <c r="D70" t="s">
         <v>106</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" s="13" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2469,7 +2493,7 @@
       <c r="D71" t="s">
         <v>108</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="13" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2485,15 +2509,18 @@
       <c r="C73" t="s">
         <v>112</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="13" t="s">
         <v>113</v>
+      </c>
+      <c r="G73" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="74" spans="2:8">
       <c r="C74" t="s">
         <v>114</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="13" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2501,7 +2528,7 @@
       <c r="C75" t="s">
         <v>116</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2512,8 +2539,11 @@
       <c r="C76" t="s">
         <v>122</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="13" t="s">
         <v>123</v>
+      </c>
+      <c r="G76" t="s">
+        <v>273</v>
       </c>
       <c r="H76" t="s">
         <v>119</v>
@@ -2523,7 +2553,7 @@
       <c r="C77" t="s">
         <v>120</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" s="13" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2531,7 +2561,7 @@
       <c r="C78" t="s">
         <v>121</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="13" t="s">
         <v>125</v>
       </c>
     </row>
@@ -2542,8 +2572,11 @@
       <c r="C79" t="s">
         <v>127</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="13" t="s">
         <v>128</v>
+      </c>
+      <c r="G79" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="2:8">
@@ -2553,15 +2586,18 @@
       <c r="C80" t="s">
         <v>132</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="13" t="s">
         <v>130</v>
+      </c>
+      <c r="G80" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="C81" t="s">
         <v>133</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="13" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2572,6 +2608,9 @@
       <c r="C82" t="s">
         <v>135</v>
       </c>
+      <c r="G82" t="s">
+        <v>273</v>
+      </c>
       <c r="H82" t="s">
         <v>136</v>
       </c>
@@ -2583,15 +2622,18 @@
       <c r="C83" t="s">
         <v>140</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" s="13" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="84" spans="2:8">
+      <c r="G83" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" ht="27">
       <c r="C84" t="s">
         <v>139</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F84" s="13" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2605,15 +2647,18 @@
       <c r="D85" t="s">
         <v>144</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F85" s="13" t="s">
         <v>145</v>
+      </c>
+      <c r="G85" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="D86" t="s">
         <v>159</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="13" t="s">
         <v>160</v>
       </c>
     </row>
@@ -2621,8 +2666,11 @@
       <c r="C87" t="s">
         <v>146</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" s="13" t="s">
         <v>147</v>
+      </c>
+      <c r="G87" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="108">
@@ -2653,7 +2701,7 @@
       <c r="D90" t="s">
         <v>154</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="13" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2664,7 +2712,7 @@
       <c r="D91" t="s">
         <v>157</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F91" s="13" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2672,7 +2720,7 @@
       <c r="C92" t="s">
         <v>166</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" s="13" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2680,7 +2728,7 @@
       <c r="C93" t="s">
         <v>161</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" s="13" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2691,7 +2739,7 @@
       <c r="D94" t="s">
         <v>165</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="13" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2708,12 +2756,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:7">
       <c r="D97" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="98" spans="1:5" s="14" customFormat="1">
+    <row r="98" spans="1:7" s="14" customFormat="1">
       <c r="C98" s="14" t="s">
         <v>253</v>
       </c>
@@ -2723,8 +2771,9 @@
       <c r="E98" s="14" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98" s="23"/>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>232</v>
       </c>
@@ -2734,38 +2783,48 @@
       <c r="C99" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="G99" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="C100" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:7">
       <c r="C101" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:7">
       <c r="B102" t="s">
         <v>243</v>
       </c>
       <c r="C102" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="G102" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="C103" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="104" spans="1:5" s="14" customFormat="1">
+    <row r="104" spans="1:7" s="14" customFormat="1">
       <c r="C104" s="14" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="F104" s="23"/>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
         <v>261</v>
+      </c>
+      <c r="G105" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
+++ b/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="276">
   <si>
     <t>测试项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1176,6 +1176,10 @@
   </si>
   <si>
     <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdb有索引，postgreSQL访问计划能够使用到该索引，且查看走Nested Loop</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1444,6 +1448,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -1462,21 +1475,80 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1488,7 +1560,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1794,7 +1866,7 @@
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="15" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1820,7 +1892,7 @@
       <c r="E2" t="s">
         <v>256</v>
       </c>
-      <c r="F2" s="22"/>
+      <c r="F2" s="16"/>
       <c r="G2" s="3" t="s">
         <v>270</v>
       </c>
@@ -1837,7 +1909,7 @@
       <c r="E3" t="s">
         <v>200</v>
       </c>
-      <c r="F3" s="22"/>
+      <c r="F3" s="16"/>
       <c r="G3" s="3"/>
       <c r="H3" s="2" t="s">
         <v>246</v>
@@ -1854,7 +1926,7 @@
       <c r="E4" t="s">
         <v>200</v>
       </c>
-      <c r="F4" s="22"/>
+      <c r="F4" s="16"/>
       <c r="G4" s="3"/>
       <c r="H4" s="2"/>
     </row>
@@ -1868,7 +1940,7 @@
       <c r="E5" t="s">
         <v>258</v>
       </c>
-      <c r="F5" s="22"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="3"/>
       <c r="H5" s="2"/>
     </row>
@@ -1980,7 +2052,7 @@
       <c r="E14" t="s">
         <v>200</v>
       </c>
-      <c r="F14" s="22"/>
+      <c r="F14" s="16"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:8">
@@ -2186,7 +2258,7 @@
       <c r="D35" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="F35" s="23"/>
+      <c r="F35" s="17"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
@@ -2320,7 +2392,7 @@
       </c>
     </row>
     <row r="52" spans="1:7" s="14" customFormat="1">
-      <c r="F52" s="23"/>
+      <c r="F52" s="17"/>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
@@ -2399,7 +2471,7 @@
       <c r="D61" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="F61" s="23"/>
+      <c r="F61" s="17"/>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
@@ -2728,6 +2800,9 @@
       <c r="C93" t="s">
         <v>161</v>
       </c>
+      <c r="E93" t="s">
+        <v>275</v>
+      </c>
       <c r="F93" s="13" t="s">
         <v>162</v>
       </c>
@@ -2771,7 +2846,7 @@
       <c r="E98" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="F98" s="23"/>
+      <c r="F98" s="17"/>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
@@ -2817,7 +2892,7 @@
       <c r="C104" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="F104" s="23"/>
+      <c r="F104" s="17"/>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
@@ -2857,11 +2932,11 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1">
       <c r="A3" s="6" t="s">
@@ -2963,11 +3038,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="17"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20"/>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1">
       <c r="A13" s="6" t="s">
@@ -3003,11 +3078,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
     </row>
     <row r="17" spans="1:3" ht="15" thickBot="1">
       <c r="A17" s="9" t="s">
@@ -3019,11 +3094,11 @@
       <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="17"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20"/>
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1">
       <c r="A19" s="6" t="s">
@@ -3084,11 +3159,11 @@
       <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="17"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="20"/>
     </row>
     <row r="26" spans="1:3" ht="15" thickBot="1">
       <c r="A26" s="6" t="s">

--- a/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
+++ b/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="280">
   <si>
     <t>测试项</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -938,10 +938,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>带条件删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>更新单条记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1180,6 +1176,25 @@
   </si>
   <si>
     <t>sdb有索引，postgreSQL访问计划能够使用到该索引，且查看走Nested Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行查询后，查看contexts数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询完成后contexts数恢复到之前值（db.snapshot(1)）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件删除</t>
+  </si>
+  <si>
+    <t>数据操作后pg连接验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pg客户端退出后，释放连接</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1837,11 +1852,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="2" max="2" width="17.375" customWidth="1"/>
     <col min="3" max="3" width="14.25" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="8.375" customWidth="1"/>
@@ -1870,7 +1885,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>5</v>
@@ -1890,11 +1905,11 @@
         <v>168</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F2" s="16"/>
       <c r="G2" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H2" s="2"/>
     </row>
@@ -1912,7 +1927,7 @@
       <c r="F3" s="16"/>
       <c r="G3" s="3"/>
       <c r="H3" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1938,7 +1953,7 @@
         <v>197</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F5" s="16"/>
       <c r="G5" s="3"/>
@@ -2277,7 +2292,7 @@
         <v>203</v>
       </c>
       <c r="G36" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2298,12 +2313,12 @@
     </row>
     <row r="39" spans="1:8">
       <c r="D39" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="D40" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F40" s="13" t="s">
         <v>213</v>
@@ -2322,73 +2337,73 @@
     </row>
     <row r="42" spans="1:8">
       <c r="B42" t="s">
+        <v>240</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="H42" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="C43" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="C44" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="B45" t="s">
+        <v>233</v>
+      </c>
+      <c r="C45" t="s">
         <v>234</v>
-      </c>
-      <c r="C45" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="C46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="B47" t="s">
+        <v>224</v>
+      </c>
+      <c r="C47" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" t="s">
         <v>225</v>
-      </c>
-      <c r="C47" t="s">
-        <v>224</v>
-      </c>
-      <c r="D47" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="D49" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="D50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="C51" t="s">
+        <v>229</v>
+      </c>
+      <c r="D51" t="s">
         <v>230</v>
-      </c>
-      <c r="D51" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="14" customFormat="1">
@@ -2402,56 +2417,56 @@
         <v>86</v>
       </c>
       <c r="D53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G53" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="B54" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E54" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="C55" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="C56" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="D57" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="B58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C58" t="s">
         <v>214</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2467,439 +2482,454 @@
         <v>217</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="14" customFormat="1">
-      <c r="D61" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="F61" s="17"/>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" t="s">
+    <row r="61" spans="1:7">
+      <c r="D61" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" s="14" customFormat="1">
+      <c r="B62" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
         <v>87</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B63" t="s">
         <v>88</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C63" t="s">
         <v>89</v>
       </c>
-      <c r="D62" t="s">
-        <v>260</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="D63" t="s">
+        <v>259</v>
+      </c>
+      <c r="E63" t="s">
         <v>90</v>
       </c>
-      <c r="F62" s="13" t="s">
+      <c r="F63" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="G62" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="54">
-      <c r="E63" t="s">
+      <c r="G63" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="54">
+      <c r="E64" t="s">
         <v>91</v>
       </c>
-      <c r="F63" s="13" t="s">
+      <c r="F64" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G63" s="13"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="E64" t="s">
+      <c r="G64" s="13"/>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="E65" t="s">
         <v>92</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F65" s="13" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8">
-      <c r="D65" t="s">
-        <v>93</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="D66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="D67" t="s">
+        <v>94</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8">
+      <c r="D68" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="27">
-      <c r="D68" t="s">
+    <row r="69" spans="2:8" ht="27">
+      <c r="D69" t="s">
         <v>96</v>
       </c>
-      <c r="F68" s="13" t="s">
+      <c r="F69" s="13" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8">
-      <c r="C69" t="s">
-        <v>103</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="70" spans="2:8">
       <c r="C70" t="s">
+        <v>103</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8">
+      <c r="C71" t="s">
         <v>105</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D71" t="s">
         <v>106</v>
       </c>
-      <c r="F70" s="13" t="s">
+      <c r="F71" s="13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="71" spans="2:8">
-      <c r="D71" t="s">
+    <row r="72" spans="2:8">
+      <c r="D72" t="s">
         <v>108</v>
       </c>
-      <c r="F71" s="13" t="s">
+      <c r="F72" s="13" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="72" spans="2:8">
-      <c r="C72" t="s">
+    <row r="73" spans="2:8">
+      <c r="C73" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="73" spans="2:8">
-      <c r="B73" t="s">
+    <row r="74" spans="2:8">
+      <c r="B74" t="s">
         <v>111</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C74" t="s">
         <v>112</v>
       </c>
-      <c r="F73" s="13" t="s">
+      <c r="F74" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="G73" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8">
-      <c r="C74" t="s">
-        <v>114</v>
-      </c>
-      <c r="F74" s="13" t="s">
-        <v>115</v>
+      <c r="G74" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="2:8">
       <c r="C75" t="s">
+        <v>114</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8">
+      <c r="C76" t="s">
         <v>116</v>
       </c>
-      <c r="F75" s="13" t="s">
+      <c r="F76" s="13" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="2:8">
-      <c r="B76" t="s">
+    <row r="77" spans="2:8">
+      <c r="B77" t="s">
         <v>118</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C77" t="s">
         <v>122</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F77" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="G76" t="s">
-        <v>273</v>
-      </c>
-      <c r="H76" t="s">
+      <c r="G77" t="s">
+        <v>272</v>
+      </c>
+      <c r="H77" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8">
-      <c r="C77" t="s">
-        <v>120</v>
-      </c>
-      <c r="F77" s="13" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="78" spans="2:8">
       <c r="C78" t="s">
+        <v>120</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="C79" t="s">
         <v>121</v>
       </c>
-      <c r="F78" s="13" t="s">
+      <c r="F79" s="13" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8">
-      <c r="B79" t="s">
-        <v>126</v>
-      </c>
-      <c r="C79" t="s">
-        <v>127</v>
-      </c>
-      <c r="F79" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G79" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="80" spans="2:8">
       <c r="B80" t="s">
+        <v>126</v>
+      </c>
+      <c r="C80" t="s">
+        <v>127</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G80" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
+      <c r="B81" t="s">
         <v>129</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C81" t="s">
         <v>132</v>
       </c>
-      <c r="F80" s="13" t="s">
+      <c r="F81" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G81" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8">
+      <c r="C82" t="s">
+        <v>133</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8">
+      <c r="B83" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C83" t="s">
+        <v>135</v>
+      </c>
+      <c r="G83" t="s">
+        <v>272</v>
+      </c>
+      <c r="H83" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
+      <c r="B84" t="s">
+        <v>137</v>
+      </c>
+      <c r="C84" t="s">
+        <v>140</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G84" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" ht="27">
+      <c r="C85" t="s">
+        <v>139</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
+      <c r="B86" t="s">
+        <v>142</v>
+      </c>
+      <c r="C86" t="s">
+        <v>143</v>
+      </c>
+      <c r="D86" t="s">
+        <v>144</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G86" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
-      <c r="C81" t="s">
-        <v>133</v>
-      </c>
-      <c r="F81" s="13" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8">
-      <c r="B82" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C82" t="s">
-        <v>135</v>
-      </c>
-      <c r="G82" t="s">
+    <row r="87" spans="2:8">
+      <c r="D87" t="s">
+        <v>159</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
+      <c r="C88" t="s">
+        <v>146</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G88" t="s">
         <v>273</v>
       </c>
-      <c r="H82" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8">
-      <c r="B83" t="s">
-        <v>137</v>
-      </c>
-      <c r="C83" t="s">
-        <v>140</v>
-      </c>
-      <c r="F83" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G83" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" ht="27">
-      <c r="C84" t="s">
-        <v>139</v>
-      </c>
-      <c r="F84" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8">
-      <c r="B85" t="s">
-        <v>142</v>
-      </c>
-      <c r="C85" t="s">
-        <v>143</v>
-      </c>
-      <c r="D85" t="s">
-        <v>144</v>
-      </c>
-      <c r="F85" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="G85" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8">
-      <c r="D86" t="s">
-        <v>159</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="87" spans="2:8">
-      <c r="C87" t="s">
-        <v>146</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="G87" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" ht="108">
-      <c r="C88" t="s">
+    </row>
+    <row r="89" spans="2:8" ht="108">
+      <c r="C89" t="s">
         <v>148</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D89" t="s">
         <v>149</v>
       </c>
-      <c r="F88" s="13" t="s">
+      <c r="F89" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G88" s="13"/>
-    </row>
-    <row r="89" spans="2:8" ht="27">
-      <c r="C89" t="s">
+      <c r="G89" s="13"/>
+    </row>
+    <row r="90" spans="2:8" ht="27">
+      <c r="C90" t="s">
         <v>151</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D90" t="s">
         <v>152</v>
       </c>
-      <c r="F89" s="13" t="s">
+      <c r="F90" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="G89" s="13"/>
-    </row>
-    <row r="90" spans="2:8">
-      <c r="D90" t="s">
+      <c r="G90" s="13"/>
+    </row>
+    <row r="91" spans="2:8">
+      <c r="D91" t="s">
         <v>154</v>
       </c>
-      <c r="F90" s="13" t="s">
+      <c r="F91" s="13" t="s">
         <v>155</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8">
-      <c r="C91" t="s">
-        <v>156</v>
-      </c>
-      <c r="D91" t="s">
-        <v>157</v>
-      </c>
-      <c r="F91" s="13" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="92" spans="2:8">
       <c r="C92" t="s">
-        <v>166</v>
+        <v>156</v>
+      </c>
+      <c r="D92" t="s">
+        <v>157</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="93" spans="2:8">
       <c r="C93" t="s">
-        <v>161</v>
-      </c>
-      <c r="E93" t="s">
-        <v>275</v>
+        <v>166</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="2:8">
       <c r="C94" t="s">
-        <v>163</v>
-      </c>
-      <c r="D94" t="s">
-        <v>165</v>
+        <v>161</v>
+      </c>
+      <c r="E94" t="s">
+        <v>274</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="95" spans="2:8">
       <c r="C95" t="s">
+        <v>163</v>
+      </c>
+      <c r="D95" t="s">
+        <v>165</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8">
+      <c r="C96" t="s">
+        <v>248</v>
+      </c>
+      <c r="D96" t="s">
         <v>249</v>
       </c>
-      <c r="D95" t="s">
+    </row>
+    <row r="97" spans="1:8">
+      <c r="D97" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="96" spans="2:8">
-      <c r="D96" t="s">
+    <row r="98" spans="1:8">
+      <c r="D98" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
-      <c r="D97" t="s">
+    <row r="99" spans="1:8">
+      <c r="C99" s="14" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" s="14" customFormat="1">
-      <c r="C98" s="14" t="s">
+      <c r="D99" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="D98" s="14" t="s">
+      <c r="E99" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="E98" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="F98" s="17"/>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" t="s">
-        <v>232</v>
-      </c>
-      <c r="B99" t="s">
+      <c r="F99" s="17"/>
+    </row>
+    <row r="100" spans="1:8" s="14" customFormat="1" ht="27">
+      <c r="B100" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="H100" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>231</v>
+      </c>
+      <c r="B101" t="s">
+        <v>236</v>
+      </c>
+      <c r="C101" t="s">
         <v>237</v>
       </c>
-      <c r="C99" t="s">
+      <c r="G101" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="C102" t="s">
         <v>238</v>
       </c>
-      <c r="G99" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="C100" t="s">
+    </row>
+    <row r="103" spans="1:8">
+      <c r="C103" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
-      <c r="C101" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="B102" t="s">
+    <row r="104" spans="1:8">
+      <c r="B104" t="s">
+        <v>242</v>
+      </c>
+      <c r="C104" t="s">
         <v>243</v>
       </c>
-      <c r="C102" t="s">
+      <c r="G104" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="C105" t="s">
         <v>244</v>
       </c>
-      <c r="G102" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="C103" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" s="14" customFormat="1">
-      <c r="C104" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="F104" s="17"/>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" t="s">
-        <v>261</v>
-      </c>
-      <c r="G105" t="s">
-        <v>273</v>
+    </row>
+    <row r="106" spans="1:8" s="14" customFormat="1">
+      <c r="C106" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="F106" s="17"/>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>260</v>
+      </c>
+      <c r="G107" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -3012,7 +3042,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1">

--- a/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
+++ b/internal_doc/05.测试设计/sdv/PostgreSQL/PG对接sequoiadb测试分析.xlsx
@@ -1496,74 +1496,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1575,7 +1507,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2763,9 +2695,6 @@
       <c r="F88" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="G88" t="s">
-        <v>273</v>
-      </c>
     </row>
     <row r="89" spans="2:8" ht="108">
       <c r="C89" t="s">
@@ -2873,6 +2802,9 @@
     <row r="100" spans="1:8" s="14" customFormat="1" ht="27">
       <c r="B100" s="17" t="s">
         <v>275</v>
+      </c>
+      <c r="G100" t="s">
+        <v>272</v>
       </c>
       <c r="H100" s="14" t="s">
         <v>276</v>
